--- a/MULTILAYER/DADES_HCB/output/GM_significant_connections.xlsx
+++ b/MULTILAYER/DADES_HCB/output/GM_significant_connections.xlsx
@@ -425,23 +425,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B156"/>
+  <dimension ref="A2:A156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="n">
-        <v>1018</v>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>002MSVIS</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>0.233230270881415</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -449,9 +441,6 @@
           <t>003MSVIS</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>0.2528910037576576</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -459,9 +448,6 @@
           <t>004MSVIS</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.2491957673297716</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -469,9 +455,6 @@
           <t>005MSVIS</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.2619619326744939</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -479,9 +462,6 @@
           <t>010MSVIS</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0.2553357792290267</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -489,9 +469,6 @@
           <t>011MSVIS</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0.252317141178826</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -499,9 +476,6 @@
           <t>012MSVIS</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.2593908588392897</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -509,9 +483,6 @@
           <t>017MSVIS</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.2614386965957495</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -519,9 +490,6 @@
           <t>018MSVIS</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0.2600223506584612</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -529,9 +497,6 @@
           <t>019MSVIS</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0.2582541735647775</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -539,9 +504,6 @@
           <t>021MSVIS</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>0.2612718023292536</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -549,9 +511,6 @@
           <t>022MSVIS</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>0.258532824941829</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -559,9 +518,6 @@
           <t>027MSVIS</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>0.258182003071158</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -569,9 +525,6 @@
           <t>030MSVIS</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0.254559946422616</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -579,9 +532,6 @@
           <t>031MSVIS</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>0.2383263345532699</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -589,9 +539,6 @@
           <t>032MSVIS</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>0.2517262452623151</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -599,9 +546,6 @@
           <t>033MSVIS</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>0.2633241507415665</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -609,9 +553,6 @@
           <t>035MSVIS</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0.2564408899125801</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -619,9 +560,6 @@
           <t>036MSVIS</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>0.2475389768994491</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -629,9 +567,6 @@
           <t>038MSVIS</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0.2584200585455488</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -639,9 +574,6 @@
           <t>039MSVIS</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>0.2496333009473416</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -649,9 +581,6 @@
           <t>040MSVIS</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0.2537750923044995</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -659,9 +588,6 @@
           <t>041MSVIS</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0.2530488767124516</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -669,9 +595,6 @@
           <t>042MSVIS</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>0.2566303374583327</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -679,9 +602,6 @@
           <t>043MSVIS</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>0.2593322203132251</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -689,9 +609,6 @@
           <t>044MSVIS</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -699,9 +616,6 @@
           <t>046MSVIS</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>0.2521016389836921</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -709,9 +623,6 @@
           <t>047MSVIS</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>0.2545328824875063</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -719,9 +630,6 @@
           <t>048MSVIS</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0.2620746990707741</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -729,9 +637,6 @@
           <t>050MSVIS</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>0.2646222103409969</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -739,9 +644,6 @@
           <t>053MSVIS</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0.2592916244105603</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -749,9 +651,6 @@
           <t>054MSVIS</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0.1915368487259141</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -759,9 +658,6 @@
           <t>055MSVIS</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0.260919971172858</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -769,9 +665,6 @@
           <t>056MSVIS</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0.2555918773268254</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -779,9 +672,6 @@
           <t>058MSVIS</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0.2564905071269427</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -789,9 +679,6 @@
           <t>059MSVIS</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0.6730881769200601</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -799,9 +686,6 @@
           <t>061MSVIS</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>0.259918605573883</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -809,9 +693,6 @@
           <t>062MSVIS</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>0.1293221771792762</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -819,9 +700,6 @@
           <t>063MSVIS</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>0.2605726506723115</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -829,9 +707,6 @@
           <t>064MSVIS</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0.2519753406198569</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -839,9 +714,6 @@
           <t>065MSVIS</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>0.2599130856323094</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -849,9 +721,6 @@
           <t>066MSVIS</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>0.250955932397478</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -859,9 +728,6 @@
           <t>067MSVIS</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0.2642353032235181</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -869,9 +735,6 @@
           <t>070MSVIS</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>0.229196490071199</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -879,9 +742,6 @@
           <t>071MSVIS</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>0.2608387793675366</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -889,9 +749,6 @@
           <t>072MSVIS</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>0.2607305236271054</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -899,9 +756,6 @@
           <t>073MSVIS</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>0.2542983283832439</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -909,9 +763,6 @@
           <t>074MSVIS</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0.2564183366333233</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -919,9 +770,6 @@
           <t>075MSVIS</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>0.2466246934945674</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -929,9 +777,6 @@
           <t>076MSVIS</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0.2411138626448378</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -939,9 +784,6 @@
           <t>077MSVIS</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>0.2531661537645847</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -949,9 +791,6 @@
           <t>078MSVIS</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0.250869220650579</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -959,9 +798,6 @@
           <t>079MSVIS</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0.2452095969892717</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -969,9 +805,6 @@
           <t>080MSVIS</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>0.2560755267886295</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -979,9 +812,6 @@
           <t>082MSVIS</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>0.2595792970993178</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -989,9 +819,6 @@
           <t>084MSVIS</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>0.2645239851979961</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -999,9 +826,6 @@
           <t>086MSVIS</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0.2585553782210859</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1009,9 +833,6 @@
           <t>087MSVIS</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>0.258033151428066</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1019,9 +840,6 @@
           <t>088MSVIS</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>0.2521866970045953</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1029,9 +847,6 @@
           <t>089MSVIS</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>0.2365753045912945</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1039,9 +854,6 @@
           <t>090MSVIS</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>0.2369727343390036</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1049,9 +861,6 @@
           <t>091MSVIS</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>0.2338153757877627</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1059,9 +868,6 @@
           <t>094MSVIS</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>0.2388562408835503</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1069,9 +875,6 @@
           <t>095MSVIS</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>0.2547664273060481</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1079,9 +882,6 @@
           <t>096MSVIS</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>0.2406710389357284</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1089,9 +889,6 @@
           <t>097MSVIS</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0.2565807202439701</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1099,9 +896,6 @@
           <t>099MSVIS</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0.2635080783457416</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1109,9 +903,6 @@
           <t>100MSVIS</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>0.2620160605447095</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1119,9 +910,6 @@
           <t>103MSVIS</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>0.2387348040161925</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1129,9 +917,6 @@
           <t>104MSVIS</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>0.2451875175588448</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1139,9 +924,6 @@
           <t>105MSVIS</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>0.2433438851180891</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1149,9 +931,6 @@
           <t>107MSVIS</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>0.2385747281455899</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1159,9 +938,6 @@
           <t>108MSVIS</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>0.2674651955104144</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1169,9 +945,6 @@
           <t>109MSVIS</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>0.2389279990324403</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -1179,9 +952,6 @@
           <t>110MSVIS</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0.2573339997711239</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1189,9 +959,6 @@
           <t>111MSVIS</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>0.2465976295594576</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1199,9 +966,6 @@
           <t>112MSVIS</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>0.2446907303742097</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1209,9 +973,6 @@
           <t>113MSVIS</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>0.2411304222176555</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1219,9 +980,6 @@
           <t>119MSVIS</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>0.2460375756303303</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1229,9 +987,6 @@
           <t>120MSVIS</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>0.2405784364569531</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -1239,9 +994,6 @@
           <t>121MSVIS</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>0.273878271095478</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1249,9 +1001,6 @@
           <t>122MSVIS</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>0.2634147956304632</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1259,9 +1008,6 @@
           <t>123MSVIS</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>0.2748971967752935</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1269,9 +1015,6 @@
           <t>126MSVIS</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>0.2570669130389474</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -1279,9 +1022,6 @@
           <t>c001MSVIS</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>0.2669355597007362</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -1289,9 +1029,6 @@
           <t>c027MSVIS</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>0.2748990848400607</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -1299,9 +1036,6 @@
           <t>c029MSVIS</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>0.2602518699262937</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -1309,9 +1043,6 @@
           <t>c030MSVIS</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>0.2591076941362499</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -1319,9 +1050,6 @@
           <t>c031MSVIS</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>0.2636748926096624</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -1329,9 +1057,6 @@
           <t>c032MSVIS</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>0.2654160661929755</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -1339,9 +1064,6 @@
           <t>c033MSVIS</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0.2668635835842065</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -1349,9 +1071,6 @@
           <t>c034MSVIS</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>0.2664483122014804</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -1359,9 +1078,6 @@
           <t>c035MSVIS</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>0.2612188590032258</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -1369,9 +1085,6 @@
           <t>c036MSVIS</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>0.2724282201128073</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -1379,9 +1092,6 @@
           <t>FIS_029</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0.2511409188137681</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -1389,9 +1099,6 @@
           <t>FIS_041</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>0.2339942946627019</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -1399,9 +1106,6 @@
           <t>FIS_047</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0.2312889620395415</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -1409,9 +1113,6 @@
           <t>FIS_048</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>0.2481207747871587</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -1419,9 +1120,6 @@
           <t>FIS_049</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>0.2564748828607664</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -1429,9 +1127,6 @@
           <t>FIS_056</t>
         </is>
       </c>
-      <c r="B101" t="n">
-        <v>0.2618088469077574</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -1439,9 +1134,6 @@
           <t>FIS_057</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>0.2399533960485364</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -1449,9 +1141,6 @@
           <t>FIS_059</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>0.2488920481272883</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -1459,9 +1148,6 @@
           <t>FIS_063</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>0.2467063101753776</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -1469,9 +1155,6 @@
           <t>FIS_065</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>0.2505951515429691</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -1479,9 +1162,6 @@
           <t>FIS_067</t>
         </is>
       </c>
-      <c r="B106" t="n">
-        <v>0.2597872988899479</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -1489,9 +1169,6 @@
           <t>FIS_068</t>
         </is>
       </c>
-      <c r="B107" t="n">
-        <v>0.2335152933251516</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -1499,9 +1176,6 @@
           <t>FIS_069</t>
         </is>
       </c>
-      <c r="B108" t="n">
-        <v>0.2590728562169859</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -1509,9 +1183,6 @@
           <t>FIS_070</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>0.2540392828393082</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -1519,9 +1190,6 @@
           <t>FIS_071</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>0.2460180401019721</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -1529,9 +1197,6 @@
           <t>FIS_072</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>0.2257033193236634</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -1539,9 +1204,6 @@
           <t>FIS_073</t>
         </is>
       </c>
-      <c r="B112" t="n">
-        <v>0.2504751881412396</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -1549,9 +1211,6 @@
           <t>FIS_074</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>0.2424440101378224</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -1559,9 +1218,6 @@
           <t>FIS_075</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -1569,9 +1225,6 @@
           <t>FIS_076</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>0.237239944758642</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -1579,9 +1232,6 @@
           <t>FIS_078</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>0.249369232865506</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -1589,9 +1239,6 @@
           <t>FIS_079</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>0.2466594147742839</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -1599,9 +1246,6 @@
           <t>FIS_080</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>0.2634551196562706</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -1609,9 +1253,6 @@
           <t>FIS_082</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>0.2520177348214916</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -1619,9 +1260,6 @@
           <t>FIS_083</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>0.2258169806579986</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -1629,9 +1267,6 @@
           <t>FIS_084</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0.2443618320873777</v>
-      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -1639,9 +1274,6 @@
           <t>FIS_085</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>0.2594219588867255</v>
-      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -1649,9 +1281,6 @@
           <t>FIS_086</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>0.2468542627760034</v>
-      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -1659,9 +1288,6 @@
           <t>FIS_088</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0.2425270134045465</v>
-      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -1669,9 +1295,6 @@
           <t>FIS_089</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>0.2551596588491776</v>
-      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -1679,9 +1302,6 @@
           <t>FIS_090</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>0.2479096894519709</v>
-      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -1689,9 +1309,6 @@
           <t>FIS_091</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>0.2580499042079764</v>
-      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -1699,9 +1316,6 @@
           <t>FIS_092</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>0.2535016342352434</v>
-      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -1709,9 +1323,6 @@
           <t>FIS_093</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>0.2635768996573472</v>
-      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -1719,9 +1330,6 @@
           <t>FIS_094</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>0.2584558375448837</v>
-      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -1729,9 +1337,6 @@
           <t>FIS_095</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>0.2501910348054016</v>
-      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -1739,9 +1344,6 @@
           <t>FIS_097</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>0.2580011922075429</v>
-      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -1749,9 +1351,6 @@
           <t>FIS_098</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>0.2552083708496038</v>
-      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -1759,9 +1358,6 @@
           <t>FIS_099</t>
         </is>
       </c>
-      <c r="B134" t="n">
-        <v>0.2486890814588346</v>
-      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -1769,9 +1365,6 @@
           <t>FIS_100</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>0.2486809627921005</v>
-      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -1779,9 +1372,6 @@
           <t>FIS_102</t>
         </is>
       </c>
-      <c r="B136" t="n">
-        <v>0.2555980668530357</v>
-      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -1789,9 +1379,6 @@
           <t>FIS_103</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>0.2478510421854636</v>
-      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -1799,9 +1386,6 @@
           <t>FIS_104</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>0.2444087274884642</v>
-      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -1809,9 +1393,6 @@
           <t>FIS_105</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>0.24000210804897</v>
-      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -1819,9 +1400,6 @@
           <t>FIS_106</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>0.2365435560184951</v>
-      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -1829,9 +1407,6 @@
           <t>FIS_107</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>0.2423402840695683</v>
-      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -1839,9 +1414,6 @@
           <t>FIS_112</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>0.2322226087144398</v>
-      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -1849,9 +1421,6 @@
           <t>FIS_113</t>
         </is>
       </c>
-      <c r="B143" t="n">
-        <v>0.2408870427234275</v>
-      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -1859,9 +1428,6 @@
           <t>FIS_115</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>0.249273625463986</v>
-      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -1869,9 +1435,6 @@
           <t>FIS_116</t>
         </is>
       </c>
-      <c r="B145" t="n">
-        <v>0.2523668374912385</v>
-      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -1879,9 +1442,6 @@
           <t>FIS_117</t>
         </is>
       </c>
-      <c r="B146" t="n">
-        <v>0.2516830528858875</v>
-      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -1889,9 +1449,6 @@
           <t>FIS_118</t>
         </is>
       </c>
-      <c r="B147" t="n">
-        <v>0.2474225694476793</v>
-      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -1899,9 +1456,6 @@
           <t>FIS_121</t>
         </is>
       </c>
-      <c r="B148" t="n">
-        <v>0.2429329467414537</v>
-      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -1909,9 +1463,6 @@
           <t>FIS_122</t>
         </is>
       </c>
-      <c r="B149" t="n">
-        <v>0.2450681560935984</v>
-      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -1919,9 +1470,6 @@
           <t>FIS_123</t>
         </is>
       </c>
-      <c r="B150" t="n">
-        <v>0.2370938087573559</v>
-      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -1929,9 +1477,6 @@
           <t>FIS_124</t>
         </is>
       </c>
-      <c r="B151" t="n">
-        <v>0.2543216195758065</v>
-      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -1939,9 +1484,6 @@
           <t>FIS_125</t>
         </is>
       </c>
-      <c r="B152" t="n">
-        <v>0.2523262441575463</v>
-      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -1949,9 +1491,6 @@
           <t>FIS_126</t>
         </is>
       </c>
-      <c r="B153" t="n">
-        <v>0.2377514207631503</v>
-      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -1959,9 +1498,6 @@
           <t>FIS_127</t>
         </is>
       </c>
-      <c r="B154" t="n">
-        <v>0.2596574002221372</v>
-      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -1969,18 +1505,12 @@
           <t>FIS_128</t>
         </is>
       </c>
-      <c r="B155" t="n">
-        <v>0.2485185894573319</v>
-      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
           <t>FIS_129</t>
         </is>
-      </c>
-      <c r="B156" t="n">
-        <v>0.2321107639794444</v>
       </c>
     </row>
   </sheetData>
